--- a/Results/Ammonia economics.xlsx
+++ b/Results/Ammonia economics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20407"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75394F2-4825-43D8-9084-154F6146EE0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A4CFBF-842F-42FB-9707-0FF2DE7D707B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="3" xr2:uid="{741FF5BF-5CBD-4A41-8A6D-60044BC89C80}"/>
   </bookViews>
@@ -17,7 +17,8 @@
     <sheet name="2030" sheetId="5" r:id="rId2"/>
     <sheet name="2040" sheetId="6" r:id="rId3"/>
     <sheet name="2050" sheetId="7" r:id="rId4"/>
-    <sheet name="Overall" sheetId="8" r:id="rId5"/>
+    <sheet name="H2 and CO2 costs" sheetId="9" r:id="rId5"/>
+    <sheet name="Overall" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="59">
   <si>
     <t>ammonia</t>
   </si>
@@ -259,13 +260,44 @@
   <si>
     <t>Wind 2050</t>
   </si>
+  <si>
+    <t>Solar hydrogen</t>
+  </si>
+  <si>
+    <t>Solar electricity</t>
+  </si>
+  <si>
+    <t>Wind electricity</t>
+  </si>
+  <si>
+    <t>Wind hydrogen</t>
+  </si>
+  <si>
+    <t>CAPEX</t>
+  </si>
+  <si>
+    <t>Solar hydrogen low</t>
+  </si>
+  <si>
+    <t>Solar hydrogen high</t>
+  </si>
+  <si>
+    <t>Wind hydrogen low</t>
+  </si>
+  <si>
+    <t>Wind hydrogen high</t>
+  </si>
+  <si>
+    <t>Avg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -318,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -333,6 +365,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -351,6 +391,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>171291</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>2824</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BD1B119-A0A1-4DA8-BC3C-6BEE6CCF5A44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5086191" y="66675"/>
+          <a:ext cx="6420009" cy="4127149"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>161395</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>113815</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3BF760F-1DBA-48C5-9AB6-BEBFF8E5D226}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6324600" y="4429125"/>
+          <a:ext cx="4238095" cy="3876190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -650,7 +783,1433 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEB3379-AAE6-44DB-9440-CE58FA411FEA}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:V51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3">
+        <f>SUM(D3:D12)</f>
+        <v>0.27850023468199292</v>
+      </c>
+      <c r="E2" s="3">
+        <f t="shared" ref="E2:F2" si="0">SUM(E3:E12)</f>
+        <v>0.23990011734099648</v>
+      </c>
+      <c r="F2" s="3">
+        <f t="shared" si="0"/>
+        <v>0.31710035202298942</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.62178</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3">
+        <f>$B3*O3</f>
+        <v>4.4684710623572724E-2</v>
+      </c>
+      <c r="E3" s="3">
+        <f>$B3*P3</f>
+        <v>2.2342355311786362E-2</v>
+      </c>
+      <c r="F3" s="3">
+        <f>$B3*Q3</f>
+        <v>6.7027065935359093E-2</v>
+      </c>
+      <c r="N3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3">
+        <v>7.1865789545454542E-2</v>
+      </c>
+      <c r="P3" s="3">
+        <f>O3*0.5</f>
+        <v>3.5932894772727271E-2</v>
+      </c>
+      <c r="Q3" s="3">
+        <f>O3*1.5</f>
+        <v>0.10779868431818182</v>
+      </c>
+      <c r="R3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>13.952</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" ref="D4:D6" si="1">$B4*O4</f>
+        <v>2.7395396058420219E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" ref="E4:E6" si="2">$B4*P4</f>
+        <v>1.3697698029210109E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" ref="F4:F6" si="3">$B4*Q4</f>
+        <v>4.109309408763033E-2</v>
+      </c>
+      <c r="N4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O4" s="3">
+        <f>1.96354616244411/1000</f>
+        <v>1.9635461624441099E-3</v>
+      </c>
+      <c r="P4" s="3">
+        <f t="shared" ref="P4:P5" si="4">O4*0.5</f>
+        <v>9.8177308122205493E-4</v>
+      </c>
+      <c r="Q4" s="3">
+        <f t="shared" ref="Q4:Q5" si="5">O4*1.5</f>
+        <v>2.9453192436661646E-3</v>
+      </c>
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="9">
+        <f>O4*1000</f>
+        <v>1.96354616244411</v>
+      </c>
+      <c r="U4" s="9">
+        <f t="shared" ref="U4:V4" si="6">P4*1000</f>
+        <v>0.98177308122205498</v>
+      </c>
+      <c r="V4" s="9">
+        <f t="shared" si="6"/>
+        <v>2.9453192436661646</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>4.9231999999999998E-2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="1"/>
+        <v>5.1201279999999998E-3</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="2"/>
+        <v>2.5600639999999999E-3</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="3"/>
+        <v>7.6801920000000006E-3</v>
+      </c>
+      <c r="N5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0.10400000000000001</v>
+      </c>
+      <c r="P5" s="3">
+        <f t="shared" si="4"/>
+        <v>5.2000000000000005E-2</v>
+      </c>
+      <c r="Q5" s="3">
+        <f t="shared" si="5"/>
+        <v>0.15600000000000003</v>
+      </c>
+      <c r="R5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="3">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="P6" s="3">
+        <v>8.34</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="R6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" ref="D7" si="7">$B7*O7</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" ref="E7" si="8">$B7*P7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" ref="F7" si="9">$B7*Q7</f>
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="3">
+        <v>6.88</v>
+      </c>
+      <c r="P7" s="3">
+        <v>5.23</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>8.48</v>
+      </c>
+      <c r="R7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" ref="D8:F10" si="10">$B8*O8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
+        <f>91/1000*596.2/607.5</f>
+        <v>8.9307325102880669E-2</v>
+      </c>
+      <c r="P8" s="3">
+        <f>O8*0.5</f>
+        <v>4.4653662551440335E-2</v>
+      </c>
+      <c r="Q8" s="3">
+        <f>O8*1.5</f>
+        <v>0.13396098765432102</v>
+      </c>
+      <c r="R8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1.4326000000000001</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="3">
+        <f>O13</f>
+        <v>0.1331</v>
+      </c>
+      <c r="E11" s="3">
+        <f>D11</f>
+        <v>0.1331</v>
+      </c>
+      <c r="F11" s="3">
+        <f>E11</f>
+        <v>0.1331</v>
+      </c>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3">
+        <f>O14</f>
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <f>D12</f>
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="F12" s="3">
+        <f>E12</f>
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+    </row>
+    <row r="13" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="N13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.1331</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" s="3">
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3">
+        <f>SUM(D16:D25)</f>
+        <v>0.29807757324199291</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" ref="E15" si="11">SUM(E16:E25)</f>
+        <v>0.24968878662099647</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" ref="F15" si="12">SUM(F16:F25)</f>
+        <v>0.3464663598629894</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.62178</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" ref="D16:F23" si="13">$B16*O3</f>
+        <v>4.4684710623572724E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="13"/>
+        <v>2.2342355311786362E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="13"/>
+        <v>6.7027065935359093E-2</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+    </row>
+    <row r="17" spans="1:20" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3">
+        <v>13.952</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" si="13"/>
+        <v>2.7395396058420219E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="13"/>
+        <v>1.3697698029210109E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="13"/>
+        <v>4.109309408763033E-2</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O17" s="3">
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.23747563999999999</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3">
+        <f t="shared" si="13"/>
+        <v>2.4697466560000002E-2</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="13"/>
+        <v>1.2348733280000001E-2</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="13"/>
+        <v>3.7046199840000002E-2</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O18" s="3">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.14326</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="3">
+        <f>O13</f>
+        <v>0.1331</v>
+      </c>
+      <c r="E24" s="3">
+        <f>D24</f>
+        <v>0.1331</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" ref="F24:F25" si="14">E24</f>
+        <v>0.1331</v>
+      </c>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="3">
+        <f>O14</f>
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" ref="E25" si="15">D25</f>
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="F25" s="3">
+        <f t="shared" si="14"/>
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B26" s="7"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="3">
+        <f>SUM(D29:D38)</f>
+        <v>1.8823294699588478</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" ref="E28" si="16">SUM(E29:E38)</f>
+        <v>1.6621447349794238</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" ref="F28" si="17">SUM(F29:F38)</f>
+        <v>3.1233142049382718</v>
+      </c>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <f t="shared" ref="D29:F36" si="18">$B29*O3</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3">
+        <f t="shared" si="18"/>
+        <v>5.7824000000000007E-2</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="18"/>
+        <v>2.8912000000000004E-2</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="18"/>
+        <v>8.6736000000000021E-2</v>
+      </c>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="3">
+        <f t="shared" si="18"/>
+        <v>1.6227199999999999</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="18"/>
+        <v>1.4678399999999998</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="18"/>
+        <v>2.7984</v>
+      </c>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="3">
+        <f t="shared" si="18"/>
+        <v>7.2785469958847743E-2</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="18"/>
+        <v>3.6392734979423871E-2</v>
+      </c>
+      <c r="F34" s="3">
+        <f t="shared" si="18"/>
+        <v>0.10917820493827163</v>
+      </c>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+    </row>
+    <row r="35" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+    </row>
+    <row r="36" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="3">
+        <f>O17</f>
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="E37" s="3">
+        <f>D37</f>
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="F37" s="3">
+        <f t="shared" ref="F37:F38" si="19">E37</f>
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="3">
+        <f>O18</f>
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" ref="E38" si="20">D38</f>
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="F38" s="3">
+        <f t="shared" si="19"/>
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="3">
+        <f>SUM(D42:D51)</f>
+        <v>1.4704894699588478</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" ref="E41" si="21">SUM(E42:E51)</f>
+        <v>1.114784734979424</v>
+      </c>
+      <c r="F41" s="3">
+        <f t="shared" ref="F41" si="22">SUM(F42:F51)</f>
+        <v>1.8173942049382716</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" s="3">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="3">
+        <f t="shared" ref="D42:F49" si="23">$B42*O3</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" s="3">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="3">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="3">
+        <f t="shared" si="23"/>
+        <v>5.7824000000000007E-2</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" si="23"/>
+        <v>2.8912000000000004E-2</v>
+      </c>
+      <c r="F44" s="3">
+        <f t="shared" si="23"/>
+        <v>8.6736000000000021E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="3">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" s="3">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="3">
+        <f t="shared" si="23"/>
+        <v>1.21088</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="23"/>
+        <v>0.92048000000000008</v>
+      </c>
+      <c r="F46" s="3">
+        <f t="shared" si="23"/>
+        <v>1.49248</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="3">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3">
+        <f t="shared" si="23"/>
+        <v>7.2785469958847743E-2</v>
+      </c>
+      <c r="E47" s="3">
+        <f t="shared" si="23"/>
+        <v>3.6392734979423871E-2</v>
+      </c>
+      <c r="F47" s="3">
+        <f t="shared" si="23"/>
+        <v>0.10917820493827163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="3">
+        <v>0</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" s="3">
+        <v>0</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="3">
+        <f>O17</f>
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="E50" s="3">
+        <f>D50</f>
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="F50" s="3">
+        <f t="shared" ref="F50:F51" si="24">E50</f>
+        <v>7.9899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="3">
+        <f>O18</f>
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" ref="E51" si="25">D51</f>
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="F51" s="3">
+        <f t="shared" si="24"/>
+        <v>4.9099999999999998E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="N16:R16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="N12:R12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D905A7F-9CAF-46F0-9748-9A9C974BB09A}">
+  <dimension ref="A1:V51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -662,12 +2221,12 @@
     <col min="18" max="18" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
       <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
@@ -677,15 +2236,15 @@
       <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -697,15 +2256,15 @@
       </c>
       <c r="D2" s="3">
         <f>SUM(D3:D12)</f>
-        <v>0.31570996150112268</v>
+        <v>0.33926632909851934</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:F2" si="0">SUM(E3:E12)</f>
-        <v>0.25716108259566028</v>
+        <v>0.27857929744686316</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>0.40751385184135536</v>
+        <v>0.39995336075017546</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>18</v>
@@ -720,7 +2279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -732,36 +2291,35 @@
       </c>
       <c r="D3" s="3">
         <f>$B3*O3</f>
-        <v>6.9994868932800006E-2</v>
+        <v>7.2099967866054548E-2</v>
       </c>
       <c r="E3" s="3">
         <f>$B3*P3</f>
-        <v>3.4108488036000001E-2</v>
+        <v>3.6049983933027274E-2</v>
       </c>
       <c r="F3" s="3">
         <f>$B3*Q3</f>
-        <v>0.12650094203039997</v>
+        <v>0.10814995179908181</v>
       </c>
       <c r="N3" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="3">
-        <f>144.88/1000*0.777</f>
-        <v>0.11257176000000001</v>
+        <v>0.11595736090909091</v>
       </c>
       <c r="P3" s="3">
-        <f>70.6/1000*0.777</f>
-        <v>5.4856200000000001E-2</v>
+        <f>O3*0.5</f>
+        <v>5.7978680454545455E-2</v>
       </c>
       <c r="Q3" s="3">
-        <f>261.84/1000*0.777</f>
-        <v>0.20344967999999997</v>
+        <f>O3*1.5</f>
+        <v>0.17393604136363636</v>
       </c>
       <c r="R3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -772,37 +2330,49 @@
         <v>10</v>
       </c>
       <c r="D4" s="3">
-        <f t="shared" ref="D4:D6" si="1">$B4*O4</f>
-        <v>4.2916470488322721E-2</v>
+        <f t="shared" ref="D4:F7" si="1">$B4*O4</f>
+        <v>4.4203199437257819E-2</v>
       </c>
       <c r="E4" s="3">
-        <f t="shared" ref="E4:E6" si="2">$B4*P4</f>
-        <v>2.0913188959660295E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.2101599718628909E-2</v>
       </c>
       <c r="F4" s="3">
-        <f t="shared" ref="F4:F6" si="3">$B4*Q4</f>
-        <v>7.7562456050955408E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.6304799155886732E-2</v>
       </c>
       <c r="N4" t="s">
         <v>2</v>
       </c>
       <c r="O4" s="3">
-        <f>144.88/1000/47.1</f>
-        <v>3.0760084925690024E-3</v>
+        <f>3.16823390461997/1000</f>
+        <v>3.16823390461997E-3</v>
       </c>
       <c r="P4" s="3">
-        <f>70.6/1000/47.1</f>
-        <v>1.4989384288747346E-3</v>
+        <f t="shared" ref="P4:P5" si="2">O4*0.5</f>
+        <v>1.584116952309985E-3</v>
       </c>
       <c r="Q4" s="3">
-        <f>261.84/1000/47.1</f>
-        <v>5.5592356687898083E-3</v>
+        <f t="shared" ref="Q4:Q5" si="3">O4*1.5</f>
+        <v>4.7523508569299548E-3</v>
       </c>
       <c r="R4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T4" s="9">
+        <f>O4*1000</f>
+        <v>3.1682339046199699</v>
+      </c>
+      <c r="U4" s="9">
+        <f t="shared" ref="U4:V4" si="4">P4*1000</f>
+        <v>1.5841169523099849</v>
+      </c>
+      <c r="V4" s="9">
+        <f t="shared" si="4"/>
+        <v>4.7523508569299544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -814,36 +2384,35 @@
       </c>
       <c r="D5" s="3">
         <f t="shared" si="1"/>
-        <v>1.4986220800000001E-3</v>
+        <v>5.0708960000000001E-3</v>
       </c>
       <c r="E5" s="3">
-        <f t="shared" si="2"/>
-        <v>8.3940559999999998E-4</v>
+        <f t="shared" si="1"/>
+        <v>2.535448E-3</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1504537599999997E-3</v>
+        <f t="shared" si="1"/>
+        <v>7.606344000000001E-3</v>
       </c>
       <c r="N5" t="s">
         <v>3</v>
       </c>
       <c r="O5" s="3">
-        <f>30.44/1000</f>
-        <v>3.0440000000000002E-2</v>
+        <v>0.10300000000000001</v>
       </c>
       <c r="P5" s="3">
-        <f>17.05/1000</f>
-        <v>1.7049999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.1500000000000004E-2</v>
       </c>
       <c r="Q5" s="3">
-        <f>43.68/1000</f>
-        <v>4.3679999999999997E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.15450000000000003</v>
       </c>
       <c r="R5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>28</v>
       </c>
@@ -858,30 +2427,30 @@
         <v>0</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N6" t="s">
         <v>28</v>
       </c>
       <c r="O6" s="3">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="P6" s="3">
-        <v>2.7</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="Q6" s="3">
-        <v>4</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="R6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>29</v>
       </c>
@@ -892,34 +2461,34 @@
         <v>6</v>
       </c>
       <c r="D7" s="3">
-        <f t="shared" ref="D7" si="4">$B7*O7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E7" s="3">
-        <f t="shared" ref="E7" si="5">$B7*P7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <f t="shared" ref="F7" si="6">$B7*Q7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
       </c>
       <c r="O7" s="3">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="P7" s="3">
-        <v>2.2000000000000002</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -930,35 +2499,37 @@
         <v>6</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" ref="D8:F10" si="7">$B8*O8</f>
+        <f t="shared" ref="D8:F10" si="5">$B8*O8</f>
         <v>0</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N8" t="s">
         <v>4</v>
       </c>
       <c r="O8" s="3">
-        <f>91/1000*596.2/607.5</f>
-        <v>8.9307325102880669E-2</v>
+        <f>91/1000*596.2/607.5*596.2/550.8</f>
+        <v>9.6668531638230679E-2</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <f>O8*0.5</f>
+        <v>4.8334265819115339E-2</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <f>O8*1.5</f>
+        <v>0.14500279745734601</v>
       </c>
       <c r="R8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
@@ -969,15 +2540,15 @@
         <v>6</v>
       </c>
       <c r="D9" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N9" t="s">
@@ -996,7 +2567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>26</v>
       </c>
@@ -1007,15 +2578,15 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N10" t="s">
@@ -1034,7 +2605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -1046,21 +2617,21 @@
       </c>
       <c r="D11" s="3">
         <f>O13</f>
-        <v>0.1331</v>
+        <v>0.14407084241103849</v>
       </c>
       <c r="E11" s="3">
         <f>D11</f>
-        <v>0.1331</v>
+        <v>0.14407084241103849</v>
       </c>
       <c r="F11" s="3">
         <f>E11</f>
-        <v>0.1331</v>
+        <v>0.14407084241103849</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -1072,30 +2643,31 @@
       </c>
       <c r="D12" s="3">
         <f>O14</f>
-        <v>6.8199999999999997E-2</v>
+        <v>7.3821423384168486E-2</v>
       </c>
       <c r="E12" s="3">
         <f>D12</f>
-        <v>6.8199999999999997E-2</v>
+        <v>7.3821423384168486E-2</v>
       </c>
       <c r="F12" s="3">
         <f>E12</f>
-        <v>6.8199999999999997E-2</v>
-      </c>
-      <c r="N12" s="6" t="s">
+        <v>7.3821423384168486E-2</v>
+      </c>
+      <c r="N12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-    </row>
-    <row r="13" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+    </row>
+    <row r="13" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
       <c r="N13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="O13" s="3">
-        <v>0.1331</v>
+        <f>0.1331*596.2/550.8</f>
+        <v>0.14407084241103849</v>
       </c>
       <c r="P13" s="3">
         <v>0</v>
@@ -1107,12 +2679,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
       <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
@@ -1126,7 +2698,8 @@
         <v>13</v>
       </c>
       <c r="O14" s="3">
-        <v>6.8199999999999997E-2</v>
+        <f>0.0682*596.2/550.8</f>
+        <v>7.3821423384168486E-2</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1138,7 +2711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>0</v>
       </c>
@@ -1150,22 +2723,22 @@
       </c>
       <c r="D15" s="3">
         <f>SUM(D16:D25)</f>
-        <v>0.32144009790272271</v>
+        <v>0.3586554240185193</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" ref="E15" si="8">SUM(E16:E25)</f>
-        <v>0.2603706366576603</v>
+        <f t="shared" ref="E15:F15" si="6">SUM(E16:E25)</f>
+        <v>0.28827384490686314</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" ref="F15" si="9">SUM(F16:F25)</f>
-        <v>0.41573633403655536</v>
+        <f t="shared" si="6"/>
+        <v>0.42903700313017551</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>1</v>
       </c>
@@ -1176,24 +2749,24 @@
         <v>7</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" ref="D16:F23" si="10">$B16*O3</f>
-        <v>6.9994868932800006E-2</v>
+        <f t="shared" ref="D16:F23" si="7">$B16*O3</f>
+        <v>7.2099967866054548E-2</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="10"/>
-        <v>3.4108488036000001E-2</v>
+        <f t="shared" si="7"/>
+        <v>3.6049983933027274E-2</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="10"/>
-        <v>0.12650094203039997</v>
-      </c>
-      <c r="N16" s="6" t="s">
+        <f t="shared" si="7"/>
+        <v>0.10814995179908181</v>
+      </c>
+      <c r="N16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1206,22 +2779,23 @@
         <v>7</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" si="10"/>
-        <v>4.2916470488322721E-2</v>
+        <f t="shared" si="7"/>
+        <v>4.4203199437257819E-2</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="10"/>
-        <v>2.0913188959660295E-2</v>
+        <f t="shared" si="7"/>
+        <v>2.2101599718628909E-2</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="10"/>
-        <v>7.7562456050955408E-2</v>
+        <f t="shared" si="7"/>
+        <v>6.6304799155886732E-2</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="O17" s="3">
-        <v>7.9899999999999999E-2</v>
+        <f>0.0799*596.2/550.8</f>
+        <v>8.6485802469135814E-2</v>
       </c>
       <c r="P17" s="3">
         <v>0</v>
@@ -1244,22 +2818,23 @@
         <v>8</v>
       </c>
       <c r="D18" s="3">
-        <f t="shared" si="10"/>
-        <v>7.2287584816000004E-3</v>
+        <f t="shared" si="7"/>
+        <v>2.4459990920000001E-2</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="10"/>
-        <v>4.0489596619999995E-3</v>
+        <f t="shared" si="7"/>
+        <v>1.222999546E-2</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="10"/>
-        <v>1.0372935955199999E-2</v>
+        <f t="shared" si="7"/>
+        <v>3.6689986380000005E-2</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="O18" s="3">
-        <v>4.9099999999999998E-2</v>
+        <f>0.0491*596.2/550.8</f>
+        <v>5.3147095134350043E-2</v>
       </c>
       <c r="P18" s="3">
         <v>0</v>
@@ -1282,15 +2857,15 @@
         <v>6</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1305,15 +2880,15 @@
         <v>6</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1328,15 +2903,15 @@
         <v>6</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1351,15 +2926,15 @@
         <v>6</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1374,15 +2949,15 @@
         <v>6</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1398,15 +2973,15 @@
       </c>
       <c r="D24" s="3">
         <f>O13</f>
-        <v>0.1331</v>
+        <v>0.14407084241103849</v>
       </c>
       <c r="E24" s="3">
         <f>D24</f>
-        <v>0.1331</v>
+        <v>0.14407084241103849</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" ref="F24:F25" si="11">E24</f>
-        <v>0.1331</v>
+        <f t="shared" ref="F24:F25" si="8">E24</f>
+        <v>0.14407084241103849</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -1421,30 +2996,30 @@
       </c>
       <c r="D25" s="3">
         <f>O14</f>
-        <v>6.8199999999999997E-2</v>
+        <v>7.3821423384168486E-2</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" ref="E25" si="12">D25</f>
-        <v>6.8199999999999997E-2</v>
+        <f t="shared" ref="E25" si="9">D25</f>
+        <v>7.3821423384168486E-2</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="11"/>
-        <v>6.8199999999999997E-2</v>
+        <f t="shared" si="8"/>
+        <v>7.3821423384168486E-2</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
       <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
@@ -1471,15 +3046,15 @@
       </c>
       <c r="D28" s="3">
         <f>SUM(D29:D38)</f>
-        <v>0.7819101099588478</v>
+        <v>1.4496057508886437</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" ref="E28" si="13">SUM(E29:E38)</f>
-        <v>0.6136798</v>
+        <f t="shared" ref="E28:F28" si="10">SUM(E29:E38)</f>
+        <v>0.92221932424606479</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" ref="F28" si="14">SUM(F29:F38)</f>
-        <v>0.85728607999999995</v>
+        <f t="shared" si="10"/>
+        <v>1.9769921775312225</v>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -1496,15 +3071,15 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <f t="shared" ref="D29:F36" si="15">$B29*O3</f>
+        <f t="shared" ref="D29:F36" si="11">$B29*O3</f>
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O29" s="3"/>
@@ -1522,15 +3097,15 @@
         <v>10</v>
       </c>
       <c r="D30" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -1545,16 +3120,16 @@
         <v>8</v>
       </c>
       <c r="D31" s="3">
-        <f t="shared" si="15"/>
-        <v>1.6924640000000001E-2</v>
+        <f t="shared" si="11"/>
+        <v>5.7268000000000006E-2</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" si="15"/>
-        <v>9.4798E-3</v>
+        <f t="shared" si="11"/>
+        <v>2.8634000000000003E-2</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="15"/>
-        <v>2.4286080000000002E-2</v>
+        <f t="shared" si="11"/>
+        <v>8.590200000000002E-2</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -1568,16 +3143,16 @@
         <v>6</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" si="15"/>
-        <v>0.56320000000000003</v>
+        <f t="shared" si="11"/>
+        <v>1.1739199999999999</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="15"/>
-        <v>0.47520000000000001</v>
+        <f t="shared" si="11"/>
+        <v>0.71455999999999986</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="15"/>
-        <v>0.70399999999999996</v>
+        <f t="shared" si="11"/>
+        <v>1.6332799999999998</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -1591,15 +3166,15 @@
         <v>6</v>
       </c>
       <c r="D33" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -1614,16 +3189,16 @@
         <v>6</v>
       </c>
       <c r="D34" s="3">
-        <f t="shared" si="15"/>
-        <v>7.2785469958847743E-2</v>
+        <f t="shared" si="11"/>
+        <v>7.8784853285157996E-2</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>3.9392426642578998E-2</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0.11817727992773699</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -1637,15 +3212,15 @@
         <v>6</v>
       </c>
       <c r="D35" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -1660,15 +3235,15 @@
         <v>6</v>
       </c>
       <c r="D36" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -1684,21 +3259,21 @@
       </c>
       <c r="D37" s="3">
         <f>O17</f>
-        <v>7.9899999999999999E-2</v>
+        <v>8.6485802469135814E-2</v>
       </c>
       <c r="E37" s="3">
         <f>D37</f>
-        <v>7.9899999999999999E-2</v>
+        <v>8.6485802469135814E-2</v>
       </c>
       <c r="F37" s="3">
-        <f t="shared" ref="F37:F38" si="16">E37</f>
-        <v>7.9899999999999999E-2</v>
-      </c>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
+        <f t="shared" ref="F37:F38" si="12">E37</f>
+        <v>8.6485802469135814E-2</v>
+      </c>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -1712,15 +3287,15 @@
       </c>
       <c r="D38" s="3">
         <f>O18</f>
-        <v>4.9099999999999998E-2</v>
+        <v>5.3147095134350043E-2</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" ref="E38" si="17">D38</f>
-        <v>4.9099999999999998E-2</v>
+        <f t="shared" ref="E38" si="13">D38</f>
+        <v>5.3147095134350043E-2</v>
       </c>
       <c r="F38" s="3">
-        <f t="shared" si="16"/>
-        <v>4.9099999999999998E-2</v>
+        <f t="shared" si="12"/>
+        <v>5.3147095134350043E-2</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -1733,11 +3308,11 @@
       <c r="Q39" s="3"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
       <c r="D40" s="1" t="s">
         <v>24</v>
       </c>
@@ -1763,15 +3338,15 @@
       </c>
       <c r="D41" s="3">
         <f>SUM(D42:D51)</f>
-        <v>0.74671010995884779</v>
+        <v>1.2876857508886439</v>
       </c>
       <c r="E41" s="3">
-        <f t="shared" ref="E41" si="18">SUM(E42:E51)</f>
-        <v>0.52567980000000003</v>
+        <f t="shared" ref="E41:F41" si="14">SUM(E42:E51)</f>
+        <v>0.82365932424606492</v>
       </c>
       <c r="F41" s="3">
-        <f t="shared" ref="F41" si="19">SUM(F42:F51)</f>
-        <v>0.85728607999999995</v>
+        <f t="shared" si="14"/>
+        <v>1.7517121775312225</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -1785,15 +3360,15 @@
         <v>7</v>
       </c>
       <c r="D42" s="3">
-        <f t="shared" ref="D42:F49" si="20">$B42*O3</f>
+        <f t="shared" ref="D42:F49" si="15">$B42*O3</f>
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -1808,15 +3383,15 @@
         <v>10</v>
       </c>
       <c r="D43" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -1831,16 +3406,16 @@
         <v>8</v>
       </c>
       <c r="D44" s="3">
-        <f t="shared" si="20"/>
-        <v>1.6924640000000001E-2</v>
+        <f t="shared" si="15"/>
+        <v>5.7268000000000006E-2</v>
       </c>
       <c r="E44" s="3">
-        <f t="shared" si="20"/>
-        <v>9.4798E-3</v>
+        <f t="shared" si="15"/>
+        <v>2.8634000000000003E-2</v>
       </c>
       <c r="F44" s="3">
-        <f t="shared" si="20"/>
-        <v>2.4286080000000002E-2</v>
+        <f t="shared" si="15"/>
+        <v>8.590200000000002E-2</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -1854,15 +3429,15 @@
         <v>6</v>
       </c>
       <c r="D45" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -1877,16 +3452,16 @@
         <v>6</v>
       </c>
       <c r="D46" s="3">
-        <f t="shared" si="20"/>
-        <v>0.52800000000000002</v>
+        <f t="shared" si="15"/>
+        <v>1.012</v>
       </c>
       <c r="E46" s="3">
-        <f t="shared" si="20"/>
-        <v>0.38719999999999999</v>
+        <f t="shared" si="15"/>
+        <v>0.61599999999999999</v>
       </c>
       <c r="F46" s="3">
-        <f t="shared" si="20"/>
-        <v>0.70399999999999996</v>
+        <f t="shared" si="15"/>
+        <v>1.4079999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -1900,16 +3475,16 @@
         <v>6</v>
       </c>
       <c r="D47" s="3">
-        <f t="shared" si="20"/>
-        <v>7.2785469958847743E-2</v>
+        <f t="shared" si="15"/>
+        <v>7.8784853285157996E-2</v>
       </c>
       <c r="E47" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>3.9392426642578998E-2</v>
       </c>
       <c r="F47" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>0.11817727992773699</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -1923,15 +3498,15 @@
         <v>6</v>
       </c>
       <c r="D48" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -1946,15 +3521,15 @@
         <v>6</v>
       </c>
       <c r="D49" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -1970,15 +3545,15 @@
       </c>
       <c r="D50" s="3">
         <f>O17</f>
-        <v>7.9899999999999999E-2</v>
+        <v>8.6485802469135814E-2</v>
       </c>
       <c r="E50" s="3">
         <f>D50</f>
-        <v>7.9899999999999999E-2</v>
+        <v>8.6485802469135814E-2</v>
       </c>
       <c r="F50" s="3">
-        <f t="shared" ref="F50:F51" si="21">E50</f>
-        <v>7.9899999999999999E-2</v>
+        <f t="shared" ref="F50:F51" si="16">E50</f>
+        <v>8.6485802469135814E-2</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1993,1390 +3568,14 @@
       </c>
       <c r="D51" s="3">
         <f>O18</f>
-        <v>4.9099999999999998E-2</v>
+        <v>5.3147095134350043E-2</v>
       </c>
       <c r="E51" s="3">
-        <f t="shared" ref="E51" si="22">D51</f>
-        <v>4.9099999999999998E-2</v>
+        <f t="shared" ref="E51" si="17">D51</f>
+        <v>5.3147095134350043E-2</v>
       </c>
       <c r="F51" s="3">
-        <f t="shared" si="21"/>
-        <v>4.9099999999999998E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="N16:R16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="N1:R1"/>
-    <mergeCell ref="N12:R12"/>
-    <mergeCell ref="N26:R26"/>
-    <mergeCell ref="N37:R37"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D905A7F-9CAF-46F0-9748-9A9C974BB09A}">
-  <dimension ref="A1:R51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3">
-        <f>SUM(D3:D12)</f>
-        <v>0.76946912801658418</v>
-      </c>
-      <c r="E2" s="3">
-        <f t="shared" ref="E2:F2" si="0">SUM(E3:E12)</f>
-        <v>0.27375334839086729</v>
-      </c>
-      <c r="F2" s="3">
-        <f t="shared" si="0"/>
-        <v>2.6799637295658707</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.62178</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3">
-        <f>$B3*O3</f>
-        <v>0.33896397012660007</v>
-      </c>
-      <c r="E3" s="3">
-        <f>$B3*P3</f>
-        <v>3.4108488036000001E-2</v>
-      </c>
-      <c r="F3" s="3">
-        <f>$B3*Q3</f>
-        <v>1.5119384475006001</v>
-      </c>
-      <c r="N3" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="3">
-        <f>701.61/1000*0.777</f>
-        <v>0.54515097000000012</v>
-      </c>
-      <c r="P3" s="3">
-        <f>70.6/1000*0.777</f>
-        <v>5.4856200000000001E-2</v>
-      </c>
-      <c r="Q3" s="3">
-        <f>3129.51/1000*0.777</f>
-        <v>2.4316292700000002</v>
-      </c>
-      <c r="R3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
-        <v>13.952</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3">
-        <f t="shared" ref="D4:F7" si="1">$B4*O4</f>
-        <v>0.20783148025477707</v>
-      </c>
-      <c r="E4" s="3">
-        <f t="shared" si="1"/>
-        <v>2.0913188959660295E-2</v>
-      </c>
-      <c r="F4" s="3">
-        <f t="shared" si="1"/>
-        <v>0.92702597707006373</v>
-      </c>
-      <c r="N4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O4" s="3">
-        <f>701.61/1000/47.1</f>
-        <v>1.4896178343949046E-2</v>
-      </c>
-      <c r="P4" s="3">
-        <f>70.6/1000/47.1</f>
-        <v>1.4989384288747346E-3</v>
-      </c>
-      <c r="Q4" s="3">
-        <f>3129.51/1000/47.1</f>
-        <v>6.644394904458599E-2</v>
-      </c>
-      <c r="R4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3">
-        <v>4.9231999999999998E-2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3">
-        <f t="shared" si="1"/>
-        <v>4.7814118399999994E-3</v>
-      </c>
-      <c r="E5" s="3">
-        <f t="shared" si="1"/>
-        <v>8.3940559999999998E-4</v>
-      </c>
-      <c r="F5" s="3">
-        <f t="shared" si="1"/>
-        <v>2.3107039200000002E-2</v>
-      </c>
-      <c r="N5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="3">
-        <f>97.12/1000</f>
-        <v>9.7119999999999998E-2</v>
-      </c>
-      <c r="P5" s="3">
-        <f>17.05/1000</f>
-        <v>1.7049999999999999E-2</v>
-      </c>
-      <c r="Q5" s="3">
-        <f>469.35/1000</f>
-        <v>0.46935000000000004</v>
-      </c>
-      <c r="R5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="P6" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="R6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="P7" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>3</v>
-      </c>
-      <c r="R7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3">
-        <f t="shared" ref="D8:F10" si="2">$B8*O8</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
-        <f>91/1000*596.2/607.5*596.2/550.8</f>
-        <v>9.6668531638230679E-2</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1.4326000000000001</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="3">
-        <f>O13</f>
-        <v>0.14407084241103849</v>
-      </c>
-      <c r="E11" s="3">
-        <f>D11</f>
-        <v>0.14407084241103849</v>
-      </c>
-      <c r="F11" s="3">
-        <f>E11</f>
-        <v>0.14407084241103849</v>
-      </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="3">
-        <f>O14</f>
-        <v>7.3821423384168486E-2</v>
-      </c>
-      <c r="E12" s="3">
-        <f>D12</f>
-        <v>7.3821423384168486E-2</v>
-      </c>
-      <c r="F12" s="3">
-        <f>E12</f>
-        <v>7.3821423384168486E-2</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-    </row>
-    <row r="13" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="N13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O13" s="3">
-        <f>0.1331*596.2/550.8</f>
-        <v>0.14407084241103849</v>
-      </c>
-      <c r="P13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O14" s="3">
-        <f>0.0682*596.2/550.8</f>
-        <v>7.3821423384168486E-2</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="3">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="3">
-        <f>SUM(D16:D25)</f>
-        <v>0.78775135033338417</v>
-      </c>
-      <c r="E15" s="3">
-        <f t="shared" ref="E15:F15" si="3">SUM(E16:E25)</f>
-        <v>0.27696290245286725</v>
-      </c>
-      <c r="F15" s="3">
-        <f t="shared" si="3"/>
-        <v>2.7683158819998708</v>
-      </c>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="3">
-        <v>0.62178</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="3">
-        <f t="shared" ref="D16:F23" si="4">$B16*O3</f>
-        <v>0.33896397012660007</v>
-      </c>
-      <c r="E16" s="3">
-        <f t="shared" si="4"/>
-        <v>3.4108488036000001E-2</v>
-      </c>
-      <c r="F16" s="3">
-        <f t="shared" si="4"/>
-        <v>1.5119384475006001</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-    </row>
-    <row r="17" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="3">
-        <v>13.952</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="3">
-        <f t="shared" si="4"/>
-        <v>0.20783148025477707</v>
-      </c>
-      <c r="E17" s="3">
-        <f t="shared" si="4"/>
-        <v>2.0913188959660295E-2</v>
-      </c>
-      <c r="F17" s="3">
-        <f t="shared" si="4"/>
-        <v>0.92702597707006373</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O17" s="3">
-        <f>0.0799*596.2/550.8</f>
-        <v>8.6485802469135814E-2</v>
-      </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="3">
-        <v>0.23747563999999999</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3">
-        <f t="shared" si="4"/>
-        <v>2.30636341568E-2</v>
-      </c>
-      <c r="E18" s="3">
-        <f t="shared" si="4"/>
-        <v>4.0489596619999995E-3</v>
-      </c>
-      <c r="F18" s="3">
-        <f t="shared" si="4"/>
-        <v>0.111459191634</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O18" s="3">
-        <f>0.0491*596.2/550.8</f>
-        <v>5.3147095134350043E-2</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3">
-        <v>0</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E19" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="3">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="3">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="3">
-        <v>0.14326</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="3">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E23" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="3">
-        <f>O13</f>
-        <v>0.14407084241103849</v>
-      </c>
-      <c r="E24" s="3">
-        <f>D24</f>
-        <v>0.14407084241103849</v>
-      </c>
-      <c r="F24" s="3">
-        <f t="shared" ref="F24:F25" si="5">E24</f>
-        <v>0.14407084241103849</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="3">
-        <f>O14</f>
-        <v>7.3821423384168486E-2</v>
-      </c>
-      <c r="E25" s="3">
-        <f t="shared" ref="E25" si="6">D25</f>
-        <v>7.3821423384168486E-2</v>
-      </c>
-      <c r="F25" s="3">
-        <f t="shared" si="5"/>
-        <v>7.3821423384168486E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="3">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="3">
-        <f>SUM(D29:D38)</f>
-        <v>0.71241647088864379</v>
-      </c>
-      <c r="E28" s="3">
-        <f t="shared" ref="E28:F28" si="7">SUM(E29:E38)</f>
-        <v>0.4659126976034858</v>
-      </c>
-      <c r="F28" s="3">
-        <f t="shared" si="7"/>
-        <v>0.87579149760348585</v>
-      </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="3">
-        <v>0</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="3">
-        <f t="shared" ref="D29:F36" si="8">$B29*O3</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B30" s="3">
-        <v>0</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="3">
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="3">
-        <f t="shared" si="8"/>
-        <v>5.3998720000000007E-2</v>
-      </c>
-      <c r="E31" s="3">
-        <f t="shared" si="8"/>
-        <v>9.4798E-3</v>
-      </c>
-      <c r="F31" s="3">
-        <f t="shared" si="8"/>
-        <v>0.26095860000000004</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="3">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="3">
-        <f t="shared" si="8"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="E32" s="3">
-        <f t="shared" si="8"/>
-        <v>0.31679999999999997</v>
-      </c>
-      <c r="F32" s="3">
-        <f t="shared" si="8"/>
-        <v>0.47520000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="3">
-        <v>0</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="3">
-        <v>0.81499999999999995</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="3">
-        <f t="shared" si="8"/>
-        <v>7.8784853285157996E-2</v>
-      </c>
-      <c r="E34" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="3">
-        <v>0</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E35" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="3">
-        <v>0</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E36" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="3">
-        <f>O17</f>
-        <v>8.6485802469135814E-2</v>
-      </c>
-      <c r="E37" s="3">
-        <f>D37</f>
-        <v>8.6485802469135814E-2</v>
-      </c>
-      <c r="F37" s="3">
-        <f t="shared" ref="F37:F38" si="9">E37</f>
-        <v>8.6485802469135814E-2</v>
-      </c>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="3">
-        <f>O18</f>
-        <v>5.3147095134350043E-2</v>
-      </c>
-      <c r="E38" s="3">
-        <f t="shared" ref="E38" si="10">D38</f>
-        <v>5.3147095134350043E-2</v>
-      </c>
-      <c r="F38" s="3">
-        <f t="shared" si="9"/>
-        <v>5.3147095134350043E-2</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="3">
-        <v>1</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="3">
-        <f>SUM(D42:D51)</f>
-        <v>0.71241647088864379</v>
-      </c>
-      <c r="E41" s="3">
-        <f t="shared" ref="E41:F41" si="11">SUM(E42:E51)</f>
-        <v>0.4659126976034858</v>
-      </c>
-      <c r="F41" s="3">
-        <f t="shared" si="11"/>
-        <v>0.92859149760348592</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B42" s="3">
-        <v>0</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="3">
-        <f t="shared" ref="D42:F49" si="12">$B42*O3</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B43" s="3">
-        <v>0</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="3">
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="3">
-        <f t="shared" si="12"/>
-        <v>5.3998720000000007E-2</v>
-      </c>
-      <c r="E44" s="3">
-        <f t="shared" si="12"/>
-        <v>9.4798E-3</v>
-      </c>
-      <c r="F44" s="3">
-        <f t="shared" si="12"/>
-        <v>0.26095860000000004</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" s="3">
-        <v>0</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" s="3">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="3">
-        <f t="shared" si="12"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="E46" s="3">
-        <f t="shared" si="12"/>
-        <v>0.31679999999999997</v>
-      </c>
-      <c r="F46" s="3">
-        <f t="shared" si="12"/>
-        <v>0.52800000000000002</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="3">
-        <v>0.81499999999999995</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="3">
-        <f t="shared" si="12"/>
-        <v>7.8784853285157996E-2</v>
-      </c>
-      <c r="E47" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A48" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B48" s="3">
-        <v>0</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B49" s="3">
-        <v>0</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D50" s="3">
-        <f>O17</f>
-        <v>8.6485802469135814E-2</v>
-      </c>
-      <c r="E50" s="3">
-        <f>D50</f>
-        <v>8.6485802469135814E-2</v>
-      </c>
-      <c r="F50" s="3">
-        <f t="shared" ref="F50:F51" si="13">E50</f>
-        <v>8.6485802469135814E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D51" s="3">
-        <f>O18</f>
-        <v>5.3147095134350043E-2</v>
-      </c>
-      <c r="E51" s="3">
-        <f t="shared" ref="E51" si="14">D51</f>
-        <v>5.3147095134350043E-2</v>
-      </c>
-      <c r="F51" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>5.3147095134350043E-2</v>
       </c>
     </row>
@@ -3398,7 +3597,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F2BC48-4868-409B-A4B0-BA4018665A77}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -3410,12 +3609,12 @@
     <col min="18" max="18" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
       <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
@@ -3425,15 +3624,15 @@
       <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -3445,15 +3644,15 @@
       </c>
       <c r="D2" s="3">
         <f>SUM(D3:D12)</f>
-        <v>0.78742902065838227</v>
+        <v>0.36444023233124434</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:F2" si="0">SUM(E3:E12)</f>
-        <v>0.29171324103266544</v>
+        <v>0.30014619538412474</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>2.6979236222076688</v>
+        <v>0.428734269278364</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>18</v>
@@ -3468,7 +3667,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -3480,36 +3679,35 @@
       </c>
       <c r="D3" s="3">
         <f>$B3*O3</f>
-        <v>0.33896397012660007</v>
+        <v>7.6633199378590908E-2</v>
       </c>
       <c r="E3" s="3">
         <f>$B3*P3</f>
-        <v>3.4108488036000001E-2</v>
+        <v>3.8316599689295454E-2</v>
       </c>
       <c r="F3" s="3">
         <f>$B3*Q3</f>
-        <v>1.5119384475006001</v>
+        <v>0.11494979906788635</v>
       </c>
       <c r="N3" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="3">
-        <f>701.61/1000*0.777</f>
-        <v>0.54515097000000012</v>
+        <v>0.12324809318181817</v>
       </c>
       <c r="P3" s="3">
-        <f>70.6/1000*0.777</f>
-        <v>5.4856200000000001E-2</v>
+        <f>O3*0.5</f>
+        <v>6.1624046590909087E-2</v>
       </c>
       <c r="Q3" s="3">
-        <f>3129.51/1000*0.777</f>
-        <v>2.4316292700000002</v>
+        <f>O3*1.5</f>
+        <v>0.18487213977272726</v>
       </c>
       <c r="R3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -3521,36 +3719,48 @@
       </c>
       <c r="D4" s="3">
         <f t="shared" ref="D4:F7" si="1">$B4*O4</f>
-        <v>0.20783148025477707</v>
+        <v>4.6982442515648322E-2</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="1"/>
-        <v>2.0913188959660295E-2</v>
+        <v>2.3491221257824161E-2</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="1"/>
-        <v>0.92702597707006373</v>
+        <v>7.0473663773472486E-2</v>
       </c>
       <c r="N4" t="s">
         <v>2</v>
       </c>
       <c r="O4" s="3">
-        <f>701.61/1000/47.1</f>
-        <v>1.4896178343949046E-2</v>
+        <f>3.36743423994039/1000</f>
+        <v>3.3674342399403899E-3</v>
       </c>
       <c r="P4" s="3">
-        <f>70.6/1000/47.1</f>
-        <v>1.4989384288747346E-3</v>
+        <f t="shared" ref="P4:P5" si="2">O4*0.5</f>
+        <v>1.683717119970195E-3</v>
       </c>
       <c r="Q4" s="3">
-        <f>3129.51/1000/47.1</f>
-        <v>6.644394904458599E-2</v>
+        <f t="shared" ref="Q4:Q5" si="3">O4*1.5</f>
+        <v>5.0511513599105851E-3</v>
       </c>
       <c r="R4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T4" s="9">
+        <f>O4*1000</f>
+        <v>3.36743423994039</v>
+      </c>
+      <c r="U4" s="9">
+        <f t="shared" ref="U4:V4" si="4">P4*1000</f>
+        <v>1.683717119970195</v>
+      </c>
+      <c r="V4" s="9">
+        <f t="shared" si="4"/>
+        <v>5.0511513599105848</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -3562,36 +3772,35 @@
       </c>
       <c r="D5" s="3">
         <f t="shared" si="1"/>
-        <v>4.7814118399999994E-3</v>
+        <v>4.9724319999999997E-3</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="1"/>
-        <v>8.3940559999999998E-4</v>
+        <v>2.4862159999999999E-3</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="1"/>
-        <v>2.3107039200000002E-2</v>
+        <v>7.4586479999999991E-3</v>
       </c>
       <c r="N5" t="s">
         <v>3</v>
       </c>
       <c r="O5" s="3">
-        <f>97.12/1000</f>
-        <v>9.7119999999999998E-2</v>
+        <v>0.10099999999999999</v>
       </c>
       <c r="P5" s="3">
-        <f>17.05/1000</f>
-        <v>1.7049999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.0499999999999996E-2</v>
       </c>
       <c r="Q5" s="3">
-        <f>469.35/1000</f>
-        <v>0.46935000000000004</v>
+        <f t="shared" si="3"/>
+        <v>0.1515</v>
       </c>
       <c r="R5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>28</v>
       </c>
@@ -3617,19 +3826,19 @@
         <v>28</v>
       </c>
       <c r="O6" s="3">
-        <v>1.8</v>
+        <v>5.28</v>
       </c>
       <c r="P6" s="3">
-        <v>1.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q6" s="3">
-        <v>2.2000000000000002</v>
+        <v>7.32</v>
       </c>
       <c r="R6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>29</v>
       </c>
@@ -3655,19 +3864,19 @@
         <v>29</v>
       </c>
       <c r="O7" s="3">
-        <v>2</v>
+        <v>4.95</v>
       </c>
       <c r="P7" s="3">
-        <v>1.6</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="Q7" s="3">
-        <v>2.6</v>
+        <v>6.8630000000000004</v>
       </c>
       <c r="R7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -3678,15 +3887,15 @@
         <v>6</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" ref="D8:F10" si="2">$B8*O8</f>
+        <f t="shared" ref="D8:F10" si="5">$B8*O8</f>
         <v>0</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N8" t="s">
@@ -3697,16 +3906,18 @@
         <v>0.1046364897652744</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <f>O8*0.5</f>
+        <v>5.2318244882637199E-2</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <f>O8*1.5</f>
+        <v>0.1569547346479116</v>
       </c>
       <c r="R8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
@@ -3717,15 +3928,15 @@
         <v>6</v>
       </c>
       <c r="D9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N9" t="s">
@@ -3744,7 +3955,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>26</v>
       </c>
@@ -3755,15 +3966,15 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N10" t="s">
@@ -3782,7 +3993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -3808,7 +4019,7 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -3830,15 +4041,15 @@
         <f>E12</f>
         <v>7.990619575461376E-2</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-    </row>
-    <row r="13" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+    </row>
+    <row r="13" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
       <c r="N13" s="1" t="s">
         <v>11</v>
       </c>
@@ -3856,12 +4067,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
       <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
@@ -3888,7 +4099,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>0</v>
       </c>
@@ -3900,22 +4111,22 @@
       </c>
       <c r="D15" s="3">
         <f>SUM(D16:D25)</f>
-        <v>0.80571124297518226</v>
+        <v>0.38345283997124435</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" ref="E15:F15" si="3">SUM(E16:E25)</f>
-        <v>0.2949227950946654</v>
+        <f t="shared" ref="E15:F15" si="6">SUM(E16:E25)</f>
+        <v>0.30965249920412474</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="3"/>
-        <v>2.7862757746416689</v>
+        <f t="shared" si="6"/>
+        <v>0.45725318073836396</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>1</v>
       </c>
@@ -3926,24 +4137,24 @@
         <v>7</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" ref="D16:F23" si="4">$B16*O3</f>
-        <v>0.33896397012660007</v>
+        <f t="shared" ref="D16:F23" si="7">$B16*O3</f>
+        <v>7.6633199378590908E-2</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="4"/>
-        <v>3.4108488036000001E-2</v>
+        <f t="shared" si="7"/>
+        <v>3.8316599689295454E-2</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="4"/>
-        <v>1.5119384475006001</v>
-      </c>
-      <c r="N16" s="6" t="s">
+        <f t="shared" si="7"/>
+        <v>0.11494979906788635</v>
+      </c>
+      <c r="N16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -3956,16 +4167,16 @@
         <v>7</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" si="4"/>
-        <v>0.20783148025477707</v>
+        <f t="shared" si="7"/>
+        <v>4.6982442515648322E-2</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="4"/>
-        <v>2.0913188959660295E-2</v>
+        <f t="shared" si="7"/>
+        <v>2.3491221257824161E-2</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="4"/>
-        <v>0.92702597707006373</v>
+        <f t="shared" si="7"/>
+        <v>7.0473663773472486E-2</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>11</v>
@@ -3995,16 +4206,16 @@
         <v>8</v>
       </c>
       <c r="D18" s="3">
-        <f t="shared" si="4"/>
-        <v>2.30636341568E-2</v>
+        <f t="shared" si="7"/>
+        <v>2.3985039639999997E-2</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="4"/>
-        <v>4.0489596619999995E-3</v>
+        <f t="shared" si="7"/>
+        <v>1.1992519819999999E-2</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="4"/>
-        <v>0.111459191634</v>
+        <f t="shared" si="7"/>
+        <v>3.5977559459999996E-2</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>13</v>
@@ -4034,15 +4245,15 @@
         <v>6</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4057,15 +4268,15 @@
         <v>6</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4080,15 +4291,15 @@
         <v>6</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4103,15 +4314,15 @@
         <v>6</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4126,15 +4337,15 @@
         <v>6</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4157,7 +4368,7 @@
         <v>0.15594596268239136</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" ref="F24:F25" si="5">E24</f>
+        <f t="shared" ref="F24:F25" si="8">E24</f>
         <v>0.15594596268239136</v>
       </c>
     </row>
@@ -4176,27 +4387,27 @@
         <v>7.990619575461376E-2</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" ref="E25" si="6">D25</f>
+        <f t="shared" ref="E25" si="9">D25</f>
         <v>7.990619575461376E-2</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>7.990619575461376E-2</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
       <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
@@ -4223,15 +4434,15 @@
       </c>
       <c r="D28" s="3">
         <f>SUM(D29:D38)</f>
-        <v>0.60721967693502088</v>
+        <v>1.2218569569350208</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" ref="E28:F28" si="7">SUM(E29:E38)</f>
-        <v>0.40702201777632219</v>
+        <f t="shared" ref="E28:F28" si="10">SUM(E29:E38)</f>
+        <v>0.79209958735567165</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" si="7"/>
-        <v>0.79930081777632234</v>
+        <f t="shared" si="10"/>
+        <v>1.6516143265143699</v>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -4248,15 +4459,15 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <f t="shared" ref="D29:F36" si="8">$B29*O3</f>
+        <f t="shared" ref="D29:F36" si="11">$B29*O3</f>
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O29" s="3"/>
@@ -4274,15 +4485,15 @@
         <v>10</v>
       </c>
       <c r="D30" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -4297,16 +4508,16 @@
         <v>8</v>
       </c>
       <c r="D31" s="3">
-        <f t="shared" si="8"/>
-        <v>5.3998720000000007E-2</v>
+        <f t="shared" si="11"/>
+        <v>5.6155999999999998E-2</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" si="8"/>
-        <v>9.4798E-3</v>
+        <f t="shared" si="11"/>
+        <v>2.8077999999999999E-2</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="8"/>
-        <v>0.26095860000000004</v>
+        <f t="shared" si="11"/>
+        <v>8.4234000000000003E-2</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -4320,16 +4531,16 @@
         <v>6</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" si="8"/>
-        <v>0.31679999999999997</v>
+        <f t="shared" si="11"/>
+        <v>0.92927999999999999</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="8"/>
-        <v>0.24639999999999998</v>
+        <f t="shared" si="11"/>
+        <v>0.57023999999999997</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="8"/>
-        <v>0.38719999999999999</v>
+        <f t="shared" si="11"/>
+        <v>1.2883199999999999</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -4343,15 +4554,15 @@
         <v>6</v>
       </c>
       <c r="D33" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -4366,16 +4577,16 @@
         <v>6</v>
       </c>
       <c r="D34" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>8.527873915869863E-2</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>4.2639369579349315E-2</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0.12791810873804793</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -4389,15 +4600,15 @@
         <v>6</v>
       </c>
       <c r="D35" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -4412,15 +4623,15 @@
         <v>6</v>
       </c>
       <c r="D36" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -4443,14 +4654,14 @@
         <v>9.3614443413396489E-2</v>
       </c>
       <c r="F37" s="3">
-        <f t="shared" ref="F37:F38" si="9">E37</f>
+        <f t="shared" ref="F37:F38" si="12">E37</f>
         <v>9.3614443413396489E-2</v>
       </c>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -4467,11 +4678,11 @@
         <v>5.7527774362925742E-2</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" ref="E38" si="10">D38</f>
+        <f t="shared" ref="E38" si="13">D38</f>
         <v>5.7527774362925742E-2</v>
       </c>
       <c r="F38" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>5.7527774362925742E-2</v>
       </c>
       <c r="N38" s="1"/>
@@ -4485,11 +4696,11 @@
       <c r="Q39" s="3"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
       <c r="D40" s="1" t="s">
         <v>24</v>
       </c>
@@ -4515,15 +4726,15 @@
       </c>
       <c r="D41" s="3">
         <f>SUM(D42:D51)</f>
-        <v>0.64241967693502089</v>
+        <v>1.1637769569350207</v>
       </c>
       <c r="E41" s="3">
-        <f t="shared" ref="E41:F41" si="11">SUM(E42:E51)</f>
-        <v>0.4422220177763222</v>
+        <f t="shared" ref="E41:F41" si="14">SUM(E42:E51)</f>
+        <v>0.75654758735567162</v>
       </c>
       <c r="F41" s="3">
-        <f t="shared" si="11"/>
-        <v>0.86970081777632235</v>
+        <f t="shared" si="14"/>
+        <v>1.5711823265143701</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -4537,15 +4748,15 @@
         <v>7</v>
       </c>
       <c r="D42" s="3">
-        <f t="shared" ref="D42:F49" si="12">$B42*O3</f>
+        <f t="shared" ref="D42:F49" si="15">$B42*O3</f>
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4560,15 +4771,15 @@
         <v>10</v>
       </c>
       <c r="D43" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4583,16 +4794,16 @@
         <v>8</v>
       </c>
       <c r="D44" s="3">
-        <f t="shared" si="12"/>
-        <v>5.3998720000000007E-2</v>
+        <f t="shared" si="15"/>
+        <v>5.6155999999999998E-2</v>
       </c>
       <c r="E44" s="3">
-        <f t="shared" si="12"/>
-        <v>9.4798E-3</v>
+        <f t="shared" si="15"/>
+        <v>2.8077999999999999E-2</v>
       </c>
       <c r="F44" s="3">
-        <f t="shared" si="12"/>
-        <v>0.26095860000000004</v>
+        <f t="shared" si="15"/>
+        <v>8.4234000000000003E-2</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -4606,15 +4817,15 @@
         <v>6</v>
       </c>
       <c r="D45" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4629,16 +4840,16 @@
         <v>6</v>
       </c>
       <c r="D46" s="3">
-        <f t="shared" si="12"/>
-        <v>0.35199999999999998</v>
+        <f t="shared" si="15"/>
+        <v>0.87119999999999997</v>
       </c>
       <c r="E46" s="3">
-        <f t="shared" si="12"/>
-        <v>0.28160000000000002</v>
+        <f t="shared" si="15"/>
+        <v>0.53468799999999994</v>
       </c>
       <c r="F46" s="3">
-        <f t="shared" si="12"/>
-        <v>0.45760000000000001</v>
+        <f t="shared" si="15"/>
+        <v>1.2078880000000001</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -4652,16 +4863,16 @@
         <v>6</v>
       </c>
       <c r="D47" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>8.527873915869863E-2</v>
       </c>
       <c r="E47" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>4.2639369579349315E-2</v>
       </c>
       <c r="F47" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>0.12791810873804793</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -4675,15 +4886,15 @@
         <v>6</v>
       </c>
       <c r="D48" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4698,15 +4909,15 @@
         <v>6</v>
       </c>
       <c r="D49" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4729,7 +4940,7 @@
         <v>9.3614443413396489E-2</v>
       </c>
       <c r="F50" s="3">
-        <f t="shared" ref="F50:F51" si="13">E50</f>
+        <f t="shared" ref="F50:F51" si="16">E50</f>
         <v>9.3614443413396489E-2</v>
       </c>
     </row>
@@ -4748,11 +4959,11 @@
         <v>5.7527774362925742E-2</v>
       </c>
       <c r="E51" s="3">
-        <f t="shared" ref="E51" si="14">D51</f>
+        <f t="shared" ref="E51" si="17">D51</f>
         <v>5.7527774362925742E-2</v>
       </c>
       <c r="F51" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>5.7527774362925742E-2</v>
       </c>
     </row>
@@ -4774,7 +4985,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4DFB47-E18B-454B-BC6D-DB219CFDE4C8}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" style="5" bestFit="1" customWidth="1"/>
@@ -4786,12 +4997,12 @@
     <col min="18" max="18" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
       <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
@@ -4801,15 +5012,15 @@
       <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -4821,15 +5032,15 @@
       </c>
       <c r="D2" s="3">
         <f>SUM(D3:D12)</f>
-        <v>0.80686926755932653</v>
+        <v>0.38850930229280639</v>
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:F2" si="0">SUM(E3:E12)</f>
-        <v>0.31115348793360964</v>
+        <v>0.32190085381537781</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" si="0"/>
-        <v>2.7173638691086133</v>
+        <v>0.45511775077023492</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>18</v>
@@ -4844,7 +5055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -4856,36 +5067,35 @@
       </c>
       <c r="D3" s="3">
         <f>$B3*O3</f>
-        <v>0.33896397012660007</v>
+        <v>7.9655353720281818E-2</v>
       </c>
       <c r="E3" s="3">
         <f>$B3*P3</f>
-        <v>3.4108488036000001E-2</v>
+        <v>3.9827676860140909E-2</v>
       </c>
       <c r="F3" s="3">
         <f>$B3*Q3</f>
-        <v>1.5119384475006001</v>
+        <v>0.11948303058042274</v>
       </c>
       <c r="N3" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="3">
-        <f>701.61/1000*0.777</f>
-        <v>0.54515097000000012</v>
+        <v>0.12810858136363637</v>
       </c>
       <c r="P3" s="3">
-        <f>70.6/1000*0.777</f>
-        <v>5.4856200000000001E-2</v>
+        <f>O3*0.5</f>
+        <v>6.4054290681818185E-2</v>
       </c>
       <c r="Q3" s="3">
-        <f>3129.51/1000*0.777</f>
-        <v>2.4316292700000002</v>
+        <f>O3*1.5</f>
+        <v>0.19216287204545457</v>
       </c>
       <c r="R3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -4897,36 +5107,48 @@
       </c>
       <c r="D4" s="3">
         <f t="shared" ref="D4:F7" si="1">$B4*O4</f>
-        <v>0.20783148025477707</v>
+        <v>4.8835271234575234E-2</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="1"/>
-        <v>2.0913188959660295E-2</v>
+        <v>2.4417635617287617E-2</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="1"/>
-        <v>0.92702597707006373</v>
+        <v>7.3252906851862851E-2</v>
       </c>
       <c r="N4" t="s">
         <v>2</v>
       </c>
       <c r="O4" s="3">
-        <f>701.61/1000/47.1</f>
-        <v>1.4896178343949046E-2</v>
+        <f>3.50023446348733/1000</f>
+        <v>3.5002344634873302E-3</v>
       </c>
       <c r="P4" s="3">
-        <f>70.6/1000/47.1</f>
-        <v>1.4989384288747346E-3</v>
+        <f t="shared" ref="P4:P5" si="2">O4*0.5</f>
+        <v>1.7501172317436651E-3</v>
       </c>
       <c r="Q4" s="3">
-        <f>3129.51/1000/47.1</f>
-        <v>6.644394904458599E-2</v>
+        <f t="shared" ref="Q4:Q5" si="3">O4*1.5</f>
+        <v>5.2503516952309955E-3</v>
       </c>
       <c r="R4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T4" s="3">
+        <f>O4*1000</f>
+        <v>3.5002344634873301</v>
+      </c>
+      <c r="U4" s="3">
+        <f t="shared" ref="U4:V4" si="4">P4*1000</f>
+        <v>1.7501172317436651</v>
+      </c>
+      <c r="V4" s="3">
+        <f t="shared" si="4"/>
+        <v>5.2503516952309957</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -4938,36 +5160,35 @@
       </c>
       <c r="D5" s="3">
         <f t="shared" si="1"/>
-        <v>4.7814118399999994E-3</v>
+        <v>4.7262720000000001E-3</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="1"/>
-        <v>8.3940559999999998E-4</v>
+        <v>2.3631360000000001E-3</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="1"/>
-        <v>2.3107039200000002E-2</v>
+        <v>7.0894080000000002E-3</v>
       </c>
       <c r="N5" t="s">
         <v>3</v>
       </c>
       <c r="O5" s="3">
-        <f>97.12/1000</f>
-        <v>9.7119999999999998E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="P5" s="3">
-        <f>17.05/1000</f>
-        <v>1.7049999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="Q5" s="3">
-        <f>469.35/1000</f>
-        <v>0.46935000000000004</v>
+        <f t="shared" si="3"/>
+        <v>0.14400000000000002</v>
       </c>
       <c r="R5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>28</v>
       </c>
@@ -4993,19 +5214,19 @@
         <v>28</v>
       </c>
       <c r="O6" s="3">
-        <v>1.5</v>
+        <v>3.927</v>
       </c>
       <c r="P6" s="3">
-        <v>1</v>
+        <v>2.5329999999999999</v>
       </c>
       <c r="Q6" s="3">
-        <v>1.8</v>
+        <v>5.32</v>
       </c>
       <c r="R6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>29</v>
       </c>
@@ -5031,19 +5252,19 @@
         <v>29</v>
       </c>
       <c r="O7" s="3">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="P7" s="3">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" s="3">
-        <v>2.2000000000000002</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="R7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -5054,35 +5275,37 @@
         <v>6</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" ref="D8:F10" si="2">$B8*O8</f>
+        <f t="shared" ref="D8:F10" si="5">$B8*O8</f>
         <v>0</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N8" t="s">
         <v>4</v>
       </c>
       <c r="O8" s="3">
-        <f>91/1000*596.2/607.5*596.2/550.8*596.2/550.8</f>
-        <v>0.1046364897652744</v>
+        <f>91/1000*596.2/607.5*596.2/550.8*596.2/550.8*596.2/550.8</f>
+        <v>0.11326121132544772</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <f>O8*0.5</f>
+        <v>5.6630605662723862E-2</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <f>O8*1.5</f>
+        <v>0.16989181698817157</v>
       </c>
       <c r="R8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>25</v>
       </c>
@@ -5093,15 +5316,15 @@
         <v>6</v>
       </c>
       <c r="D9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N9" t="s">
@@ -5120,7 +5343,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>26</v>
       </c>
@@ -5131,15 +5354,15 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N10" t="s">
@@ -5158,7 +5381,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -5184,7 +5407,7 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
@@ -5206,15 +5429,15 @@
         <f>E12</f>
         <v>8.6492508912310695E-2</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-    </row>
-    <row r="13" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+    </row>
+    <row r="13" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
       <c r="N13" s="1" t="s">
         <v>11</v>
       </c>
@@ -5232,12 +5455,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:22" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
       <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
@@ -5264,7 +5487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>0</v>
       </c>
@@ -5276,22 +5499,22 @@
       </c>
       <c r="D15" s="3">
         <f>SUM(D16:D25)</f>
-        <v>0.82515148987612652</v>
+        <v>0.40658069173280637</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" ref="E15:F15" si="3">SUM(E16:E25)</f>
-        <v>0.3143630419956096</v>
+        <f t="shared" ref="E15:F15" si="6">SUM(E16:E25)</f>
+        <v>0.33093654853537785</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="3"/>
-        <v>2.8057160215426133</v>
+        <f t="shared" si="6"/>
+        <v>0.48222483493023488</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>1</v>
       </c>
@@ -5302,24 +5525,24 @@
         <v>7</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" ref="D16:F23" si="4">$B16*O3</f>
-        <v>0.33896397012660007</v>
+        <f t="shared" ref="D16:F23" si="7">$B16*O3</f>
+        <v>7.9655353720281818E-2</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="4"/>
-        <v>3.4108488036000001E-2</v>
+        <f t="shared" si="7"/>
+        <v>3.9827676860140909E-2</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="4"/>
-        <v>1.5119384475006001</v>
-      </c>
-      <c r="N16" s="6" t="s">
+        <f t="shared" si="7"/>
+        <v>0.11948303058042274</v>
+      </c>
+      <c r="N16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" spans="1:18" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -5332,16 +5555,16 @@
         <v>7</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" si="4"/>
-        <v>0.20783148025477707</v>
+        <f t="shared" si="7"/>
+        <v>4.8835271234575234E-2</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="4"/>
-        <v>2.0913188959660295E-2</v>
+        <f t="shared" si="7"/>
+        <v>2.4417635617287617E-2</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="4"/>
-        <v>0.92702597707006373</v>
+        <f t="shared" si="7"/>
+        <v>7.3252906851862851E-2</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>11</v>
@@ -5371,16 +5594,16 @@
         <v>8</v>
       </c>
       <c r="D18" s="3">
-        <f t="shared" si="4"/>
-        <v>2.30636341568E-2</v>
+        <f t="shared" si="7"/>
+        <v>2.2797661439999999E-2</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="4"/>
-        <v>4.0489596619999995E-3</v>
+        <f t="shared" si="7"/>
+        <v>1.1398830719999999E-2</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="4"/>
-        <v>0.111459191634</v>
+        <f t="shared" si="7"/>
+        <v>3.4196492160000001E-2</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>13</v>
@@ -5410,15 +5633,15 @@
         <v>6</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5433,15 +5656,15 @@
         <v>6</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5456,15 +5679,15 @@
         <v>6</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5479,15 +5702,15 @@
         <v>6</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5502,15 +5725,15 @@
         <v>6</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -5533,7 +5756,7 @@
         <v>0.16879989642563861</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" ref="F24:F25" si="5">E24</f>
+        <f t="shared" ref="F24:F25" si="8">E24</f>
         <v>0.16879989642563861</v>
       </c>
     </row>
@@ -5552,27 +5775,27 @@
         <v>8.6492508912310695E-2</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" ref="E25" si="6">D25</f>
+        <f t="shared" ref="E25" si="9">D25</f>
         <v>8.6492508912310695E-2</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>8.6492508912310695E-2</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
       <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
@@ -5599,15 +5822,15 @@
       </c>
       <c r="D28" s="3">
         <f>SUM(D29:D38)</f>
-        <v>0.56687765930075262</v>
+        <v>1.0004360873722939</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" ref="E28:F28" si="7">SUM(E29:E38)</f>
-        <v>0.34908000014205398</v>
+        <f t="shared" ref="E28:F28" si="10">SUM(E29:E38)</f>
+        <v>0.68225014375717397</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" si="7"/>
-        <v>0.74135880014205402</v>
+        <f t="shared" si="10"/>
+        <v>1.3184460309874138</v>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -5624,15 +5847,15 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <f t="shared" ref="D29:F36" si="8">$B29*O3</f>
+        <f t="shared" ref="D29:F36" si="11">$B29*O3</f>
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O29" s="3"/>
@@ -5650,15 +5873,15 @@
         <v>10</v>
       </c>
       <c r="D30" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5673,16 +5896,16 @@
         <v>8</v>
       </c>
       <c r="D31" s="3">
-        <f t="shared" si="8"/>
-        <v>5.3998720000000007E-2</v>
+        <f t="shared" si="11"/>
+        <v>5.3376000000000007E-2</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" si="8"/>
-        <v>9.4798E-3</v>
+        <f t="shared" si="11"/>
+        <v>2.6688000000000003E-2</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="8"/>
-        <v>0.26095860000000004</v>
+        <f t="shared" si="11"/>
+        <v>8.006400000000001E-2</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -5696,16 +5919,16 @@
         <v>6</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" si="8"/>
-        <v>0.26400000000000001</v>
+        <f t="shared" si="11"/>
+        <v>0.69115199999999999</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="8"/>
-        <v>0.17599999999999999</v>
+        <f t="shared" si="11"/>
+        <v>0.44580799999999998</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="8"/>
-        <v>0.31679999999999997</v>
+        <f t="shared" si="11"/>
+        <v>0.93632000000000004</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -5719,15 +5942,15 @@
         <v>6</v>
       </c>
       <c r="D33" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5742,16 +5965,16 @@
         <v>6</v>
       </c>
       <c r="D34" s="3">
-        <f t="shared" si="8"/>
-        <v>8.527873915869863E-2</v>
+        <f t="shared" si="11"/>
+        <v>9.2307887230239888E-2</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>4.6153943615119944E-2</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0.13846183084535982</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -5765,15 +5988,15 @@
         <v>6</v>
       </c>
       <c r="D35" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5788,15 +6011,15 @@
         <v>6</v>
       </c>
       <c r="D36" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5819,14 +6042,14 @@
         <v>0.10133066659961329</v>
       </c>
       <c r="F37" s="3">
-        <f t="shared" ref="F37:F38" si="9">E37</f>
+        <f t="shared" ref="F37:F38" si="12">E37</f>
         <v>0.10133066659961329</v>
       </c>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
@@ -5843,11 +6066,11 @@
         <v>6.2269533542440698E-2</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" ref="E38" si="10">D38</f>
+        <f t="shared" ref="E38" si="13">D38</f>
         <v>6.2269533542440698E-2</v>
       </c>
       <c r="F38" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>6.2269533542440698E-2</v>
       </c>
       <c r="N38" s="1"/>
@@ -5861,11 +6084,11 @@
       <c r="Q39" s="3"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
       <c r="D40" s="1" t="s">
         <v>24</v>
       </c>
@@ -5891,15 +6114,15 @@
       </c>
       <c r="D41" s="3">
         <f>SUM(D42:D51)</f>
-        <v>0.61967765930075258</v>
+        <v>0.92528408737229384</v>
       </c>
       <c r="E41" s="3">
-        <f t="shared" ref="E41:F41" si="11">SUM(E42:E51)</f>
-        <v>0.38428000014205399</v>
+        <f t="shared" ref="E41:F41" si="14">SUM(E42:E51)</f>
+        <v>0.65884214375717387</v>
       </c>
       <c r="F41" s="3">
-        <f t="shared" si="11"/>
-        <v>0.81175880014205404</v>
+        <f t="shared" si="14"/>
+        <v>1.1917260309874138</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -5913,15 +6136,15 @@
         <v>7</v>
       </c>
       <c r="D42" s="3">
-        <f t="shared" ref="D42:F49" si="12">$B42*O3</f>
+        <f t="shared" ref="D42:F49" si="15">$B42*O3</f>
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5936,15 +6159,15 @@
         <v>10</v>
       </c>
       <c r="D43" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5959,16 +6182,16 @@
         <v>8</v>
       </c>
       <c r="D44" s="3">
-        <f t="shared" si="12"/>
-        <v>5.3998720000000007E-2</v>
+        <f t="shared" si="15"/>
+        <v>5.3376000000000007E-2</v>
       </c>
       <c r="E44" s="3">
-        <f t="shared" si="12"/>
-        <v>9.4798E-3</v>
+        <f t="shared" si="15"/>
+        <v>2.6688000000000003E-2</v>
       </c>
       <c r="F44" s="3">
-        <f t="shared" si="12"/>
-        <v>0.26095860000000004</v>
+        <f t="shared" si="15"/>
+        <v>8.006400000000001E-2</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -5982,15 +6205,15 @@
         <v>6</v>
       </c>
       <c r="D45" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -6005,16 +6228,16 @@
         <v>6</v>
       </c>
       <c r="D46" s="3">
-        <f t="shared" si="12"/>
-        <v>0.31679999999999997</v>
+        <f t="shared" si="15"/>
+        <v>0.61599999999999999</v>
       </c>
       <c r="E46" s="3">
-        <f t="shared" si="12"/>
-        <v>0.21119999999999997</v>
+        <f t="shared" si="15"/>
+        <v>0.42239999999999994</v>
       </c>
       <c r="F46" s="3">
-        <f t="shared" si="12"/>
-        <v>0.38719999999999999</v>
+        <f t="shared" si="15"/>
+        <v>0.80959999999999988</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -6028,16 +6251,16 @@
         <v>6</v>
       </c>
       <c r="D47" s="3">
-        <f t="shared" si="12"/>
-        <v>8.527873915869863E-2</v>
+        <f t="shared" si="15"/>
+        <v>9.2307887230239888E-2</v>
       </c>
       <c r="E47" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>4.6153943615119944E-2</v>
       </c>
       <c r="F47" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>0.13846183084535982</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -6051,15 +6274,15 @@
         <v>6</v>
       </c>
       <c r="D48" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -6074,15 +6297,15 @@
         <v>6</v>
       </c>
       <c r="D49" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -6105,7 +6328,7 @@
         <v>0.10133066659961329</v>
       </c>
       <c r="F50" s="3">
-        <f t="shared" ref="F50:F51" si="13">E50</f>
+        <f t="shared" ref="F50:F51" si="16">E50</f>
         <v>0.10133066659961329</v>
       </c>
     </row>
@@ -6124,11 +6347,11 @@
         <v>6.2269533542440698E-2</v>
       </c>
       <c r="E51" s="3">
-        <f t="shared" ref="E51" si="14">D51</f>
+        <f t="shared" ref="E51" si="17">D51</f>
         <v>6.2269533542440698E-2</v>
       </c>
       <c r="F51" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>6.2269533542440698E-2</v>
       </c>
     </row>
@@ -6149,6 +6372,275 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F152BA73-7F1F-4321-B89C-D7800EFD6BD9}">
+  <dimension ref="A2:Y24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6">
+        <v>2030</v>
+      </c>
+      <c r="C2" s="6">
+        <v>2040</v>
+      </c>
+      <c r="D2" s="6">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="6">
+        <v>750</v>
+      </c>
+      <c r="C3" s="6">
+        <v>500</v>
+      </c>
+      <c r="D3" s="6">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="6">
+        <v>58</v>
+      </c>
+      <c r="C4" s="6">
+        <v>48</v>
+      </c>
+      <c r="D4" s="6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="3">
+        <f>AVERAGE(B6:B7)</f>
+        <v>6.67</v>
+      </c>
+      <c r="C5" s="3">
+        <f t="shared" ref="C5:D5" si="0">AVERAGE(C6:C7)</f>
+        <v>5.2799999999999994</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
+        <v>3.9266666666666663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="3">
+        <f>B4*3.5/50</f>
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="C6" s="3">
+        <f>C4*2.7/40</f>
+        <v>3.2400000000000007</v>
+      </c>
+      <c r="D6" s="3">
+        <f>2*D4/30</f>
+        <v>2.5333333333333332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="3">
+        <f>B4*8/50</f>
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="C7" s="3">
+        <f>C4*6.1/40</f>
+        <v>7.3199999999999985</v>
+      </c>
+      <c r="D7" s="3">
+        <f>4.2*D4/30</f>
+        <v>5.3199999999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="6">
+        <v>50</v>
+      </c>
+      <c r="C8" s="6">
+        <v>45</v>
+      </c>
+      <c r="D8" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="3">
+        <f>AVERAGE(B10:B11)</f>
+        <v>5.75</v>
+      </c>
+      <c r="C9" s="3">
+        <f t="shared" ref="C9" si="1">AVERAGE(C10:C11)</f>
+        <v>4.95</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" ref="D9" si="2">AVERAGE(D10:D11)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="C10" s="3">
+        <f>C8*2.7/40</f>
+        <v>3.0375000000000005</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="3">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3">
+        <f>C8*6.1/40</f>
+        <v>6.8624999999999998</v>
+      </c>
+      <c r="D11" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y14" s="8"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>2020</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.36153846153846153</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.62307692307692308</v>
+      </c>
+      <c r="Y15" s="8"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>2030</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.12307692307692308</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.46923076923076923</v>
+      </c>
+      <c r="Y16" s="8"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>2040</v>
+      </c>
+      <c r="B17" s="3">
+        <f>AVERAGE(B16,B18)</f>
+        <v>0.15769230769230769</v>
+      </c>
+      <c r="C17" s="3">
+        <f>AVERAGE(C16,C18)</f>
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="D17" s="3">
+        <f>AVERAGE(D16,D18)</f>
+        <v>0.43076923076923079</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>2050</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.12307692307692308</v>
+      </c>
+      <c r="C18" s="3">
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.3923076923076923</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C21" s="3"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C22" s="3"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E36BB0CB-85CA-425C-975B-ECF102D0ECEB}">
   <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6216,35 +6708,35 @@
       </c>
       <c r="B2" s="3">
         <f>'2020'!D3</f>
-        <v>6.9994868932800006E-2</v>
+        <v>4.4684710623572724E-2</v>
       </c>
       <c r="C2" s="3">
         <f>'2030'!D3</f>
-        <v>0.33896397012660007</v>
+        <v>7.2099967866054548E-2</v>
       </c>
       <c r="D2" s="3">
         <f>'2040'!D3</f>
-        <v>0.33896397012660007</v>
+        <v>7.6633199378590908E-2</v>
       </c>
       <c r="E2" s="3">
         <f>'2050'!D3</f>
-        <v>0.33896397012660007</v>
+        <v>7.9655353720281818E-2</v>
       </c>
       <c r="F2" s="3">
         <f>'2020'!D16</f>
-        <v>6.9994868932800006E-2</v>
+        <v>4.4684710623572724E-2</v>
       </c>
       <c r="G2" s="3">
         <f>'2030'!D16</f>
-        <v>0.33896397012660007</v>
+        <v>7.2099967866054548E-2</v>
       </c>
       <c r="H2" s="3">
         <f>'2040'!D16</f>
-        <v>0.33896397012660007</v>
+        <v>7.6633199378590908E-2</v>
       </c>
       <c r="I2" s="3">
         <f>'2050'!D16</f>
-        <v>0.33896397012660007</v>
+        <v>7.9655353720281818E-2</v>
       </c>
       <c r="J2" s="3">
         <f>'2020'!D29</f>
@@ -6285,35 +6777,35 @@
       </c>
       <c r="B3" s="3">
         <f>'2020'!D4</f>
-        <v>4.2916470488322721E-2</v>
+        <v>2.7395396058420219E-2</v>
       </c>
       <c r="C3" s="3">
         <f>'2030'!D4</f>
-        <v>0.20783148025477707</v>
+        <v>4.4203199437257819E-2</v>
       </c>
       <c r="D3" s="3">
         <f>'2040'!D4</f>
-        <v>0.20783148025477707</v>
+        <v>4.6982442515648322E-2</v>
       </c>
       <c r="E3" s="3">
         <f>'2050'!D4</f>
-        <v>0.20783148025477707</v>
+        <v>4.8835271234575234E-2</v>
       </c>
       <c r="F3" s="3">
         <f>'2020'!D17</f>
-        <v>4.2916470488322721E-2</v>
+        <v>2.7395396058420219E-2</v>
       </c>
       <c r="G3" s="3">
         <f>'2030'!D17</f>
-        <v>0.20783148025477707</v>
+        <v>4.4203199437257819E-2</v>
       </c>
       <c r="H3" s="3">
         <f>'2040'!D17</f>
-        <v>0.20783148025477707</v>
+        <v>4.6982442515648322E-2</v>
       </c>
       <c r="I3" s="3">
         <f>'2050'!D17</f>
-        <v>0.20783148025477707</v>
+        <v>4.8835271234575234E-2</v>
       </c>
       <c r="J3" s="3">
         <f>'2020'!D30</f>
@@ -6354,67 +6846,67 @@
       </c>
       <c r="B4" s="3">
         <f>'2020'!D5</f>
-        <v>1.4986220800000001E-3</v>
+        <v>5.1201279999999998E-3</v>
       </c>
       <c r="C4" s="3">
         <f>'2030'!D5</f>
-        <v>4.7814118399999994E-3</v>
+        <v>5.0708960000000001E-3</v>
       </c>
       <c r="D4" s="3">
         <f>'2040'!D5</f>
-        <v>4.7814118399999994E-3</v>
+        <v>4.9724319999999997E-3</v>
       </c>
       <c r="E4" s="3">
         <f>'2050'!D5</f>
-        <v>4.7814118399999994E-3</v>
+        <v>4.7262720000000001E-3</v>
       </c>
       <c r="F4" s="3">
         <f>'2020'!D18</f>
-        <v>7.2287584816000004E-3</v>
+        <v>2.4697466560000002E-2</v>
       </c>
       <c r="G4" s="3">
         <f>'2030'!D18</f>
-        <v>2.30636341568E-2</v>
+        <v>2.4459990920000001E-2</v>
       </c>
       <c r="H4" s="3">
         <f>'2040'!D18</f>
-        <v>2.30636341568E-2</v>
+        <v>2.3985039639999997E-2</v>
       </c>
       <c r="I4" s="3">
         <f>'2050'!D18</f>
-        <v>2.30636341568E-2</v>
+        <v>2.2797661439999999E-2</v>
       </c>
       <c r="J4" s="3">
         <f>'2020'!D31</f>
-        <v>1.6924640000000001E-2</v>
+        <v>5.7824000000000007E-2</v>
       </c>
       <c r="K4" s="3">
         <f>'2030'!D31</f>
-        <v>5.3998720000000007E-2</v>
+        <v>5.7268000000000006E-2</v>
       </c>
       <c r="L4" s="3">
         <f>'2040'!D31</f>
-        <v>5.3998720000000007E-2</v>
+        <v>5.6155999999999998E-2</v>
       </c>
       <c r="M4" s="3">
         <f>'2050'!D31</f>
-        <v>5.3998720000000007E-2</v>
+        <v>5.3376000000000007E-2</v>
       </c>
       <c r="N4" s="3">
         <f>'2020'!D44</f>
-        <v>1.6924640000000001E-2</v>
+        <v>5.7824000000000007E-2</v>
       </c>
       <c r="O4" s="3">
         <f>'2030'!D44</f>
-        <v>5.3998720000000007E-2</v>
+        <v>5.7268000000000006E-2</v>
       </c>
       <c r="P4" s="3">
         <f>'2040'!D44</f>
-        <v>5.3998720000000007E-2</v>
+        <v>5.6155999999999998E-2</v>
       </c>
       <c r="Q4" s="3">
         <f>'2050'!D44</f>
-        <v>5.3998720000000007E-2</v>
+        <v>5.3376000000000007E-2</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -6455,19 +6947,19 @@
       </c>
       <c r="J5" s="3">
         <f>'2020'!D32</f>
-        <v>0.56320000000000003</v>
+        <v>1.6227199999999999</v>
       </c>
       <c r="K5" s="3">
         <f>'2030'!D32</f>
-        <v>0.43999999999999995</v>
+        <v>1.1739199999999999</v>
       </c>
       <c r="L5" s="3">
         <f>'2040'!D32</f>
-        <v>0.31679999999999997</v>
+        <v>0.92927999999999999</v>
       </c>
       <c r="M5" s="3">
         <f>'2050'!D32</f>
-        <v>0.26400000000000001</v>
+        <v>0.69115199999999999</v>
       </c>
       <c r="N5" s="3">
         <f>'2020'!D45</f>
@@ -6540,19 +7032,19 @@
       </c>
       <c r="N6" s="3">
         <f>'2020'!D46</f>
-        <v>0.52800000000000002</v>
+        <v>1.21088</v>
       </c>
       <c r="O6" s="3">
         <f>'2030'!D46</f>
-        <v>0.43999999999999995</v>
+        <v>1.012</v>
       </c>
       <c r="P6" s="3">
         <f>'2040'!D46</f>
-        <v>0.35199999999999998</v>
+        <v>0.87119999999999997</v>
       </c>
       <c r="Q6" s="3">
         <f>'2050'!D46</f>
-        <v>0.31679999999999997</v>
+        <v>0.61599999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -6605,7 +7097,7 @@
       </c>
       <c r="M7" s="3">
         <f>'2050'!D34</f>
-        <v>8.527873915869863E-2</v>
+        <v>9.2307887230239888E-2</v>
       </c>
       <c r="N7" s="3">
         <f>'2020'!D47</f>
@@ -6621,7 +7113,7 @@
       </c>
       <c r="Q7" s="3">
         <f>'2050'!D47</f>
-        <v>8.527873915869863E-2</v>
+        <v>9.2307887230239888E-2</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="18" x14ac:dyDescent="0.35">
@@ -6906,67 +7398,67 @@
       </c>
       <c r="B12" s="3">
         <f>'2020'!E2</f>
-        <v>0.25716108259566028</v>
+        <v>0.23990011734099648</v>
       </c>
       <c r="C12" s="3">
         <f>'2030'!E2</f>
-        <v>0.27375334839086729</v>
+        <v>0.27857929744686316</v>
       </c>
       <c r="D12" s="3">
         <f>'2040'!E2</f>
-        <v>0.29171324103266544</v>
+        <v>0.30014619538412474</v>
       </c>
       <c r="E12" s="3">
         <f>'2050'!E2</f>
-        <v>0.31115348793360964</v>
+        <v>0.32190085381537781</v>
       </c>
       <c r="F12" s="3">
         <f>'2020'!E15</f>
-        <v>0.2603706366576603</v>
+        <v>0.24968878662099647</v>
       </c>
       <c r="G12" s="3">
         <f>'2030'!E15</f>
-        <v>0.27696290245286725</v>
+        <v>0.28827384490686314</v>
       </c>
       <c r="H12" s="3">
         <f>'2040'!E15</f>
-        <v>0.2949227950946654</v>
+        <v>0.30965249920412474</v>
       </c>
       <c r="I12" s="3">
         <f>'2050'!E15</f>
-        <v>0.3143630419956096</v>
+        <v>0.33093654853537785</v>
       </c>
       <c r="J12" s="3">
         <f>'2020'!E28</f>
-        <v>0.6136798</v>
+        <v>1.6621447349794238</v>
       </c>
       <c r="K12" s="3">
         <f>'2030'!E28</f>
-        <v>0.4659126976034858</v>
+        <v>0.92221932424606479</v>
       </c>
       <c r="L12" s="3">
         <f>'2040'!E28</f>
-        <v>0.40702201777632219</v>
+        <v>0.79209958735567165</v>
       </c>
       <c r="M12" s="3">
         <f>'2050'!E28</f>
-        <v>0.34908000014205398</v>
+        <v>0.68225014375717397</v>
       </c>
       <c r="N12" s="3">
         <f>'2020'!E41</f>
-        <v>0.52567980000000003</v>
+        <v>1.114784734979424</v>
       </c>
       <c r="O12" s="3">
         <f>'2030'!E41</f>
-        <v>0.4659126976034858</v>
+        <v>0.82365932424606492</v>
       </c>
       <c r="P12" s="3">
         <f>'2040'!E41</f>
-        <v>0.4422220177763222</v>
+        <v>0.75654758735567162</v>
       </c>
       <c r="Q12" s="3">
         <f>'2050'!E41</f>
-        <v>0.38428000014205399</v>
+        <v>0.65884214375717387</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -6975,67 +7467,67 @@
       </c>
       <c r="B13" s="3">
         <f>'2020'!F2</f>
-        <v>0.40751385184135536</v>
+        <v>0.31710035202298942</v>
       </c>
       <c r="C13" s="3">
         <f>'2030'!F2</f>
-        <v>2.6799637295658707</v>
+        <v>0.39995336075017546</v>
       </c>
       <c r="D13" s="3">
         <f>'2040'!F2</f>
-        <v>2.6979236222076688</v>
+        <v>0.428734269278364</v>
       </c>
       <c r="E13" s="3">
         <f>'2050'!F2</f>
-        <v>2.7173638691086133</v>
+        <v>0.45511775077023492</v>
       </c>
       <c r="F13" s="3">
         <f>'2020'!F15</f>
-        <v>0.41573633403655536</v>
+        <v>0.3464663598629894</v>
       </c>
       <c r="G13" s="3">
         <f>'2030'!F15</f>
-        <v>2.7683158819998708</v>
+        <v>0.42903700313017551</v>
       </c>
       <c r="H13" s="3">
         <f>'2040'!F15</f>
-        <v>2.7862757746416689</v>
+        <v>0.45725318073836396</v>
       </c>
       <c r="I13" s="3">
         <f>'2050'!F15</f>
-        <v>2.8057160215426133</v>
+        <v>0.48222483493023488</v>
       </c>
       <c r="J13" s="3">
         <f>'2020'!F28</f>
-        <v>0.85728607999999995</v>
+        <v>3.1233142049382718</v>
       </c>
       <c r="K13" s="3">
         <f>'2030'!F28</f>
-        <v>0.87579149760348585</v>
+        <v>1.9769921775312225</v>
       </c>
       <c r="L13" s="3">
         <f>'2040'!F28</f>
-        <v>0.79930081777632234</v>
+        <v>1.6516143265143699</v>
       </c>
       <c r="M13" s="3">
         <f>'2050'!F28</f>
-        <v>0.74135880014205402</v>
+        <v>1.3184460309874138</v>
       </c>
       <c r="N13" s="3">
         <f>'2020'!F41</f>
-        <v>0.85728607999999995</v>
+        <v>1.8173942049382716</v>
       </c>
       <c r="O13" s="3">
         <f>'2030'!F41</f>
-        <v>0.92859149760348592</v>
+        <v>1.7517121775312225</v>
       </c>
       <c r="P13" s="3">
         <f>'2040'!F41</f>
-        <v>0.86970081777632235</v>
+        <v>1.5711823265143701</v>
       </c>
       <c r="Q13" s="3">
         <f>'2050'!F41</f>
-        <v>0.81175880014205404</v>
+        <v>1.1917260309874138</v>
       </c>
     </row>
   </sheetData>
